--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -21256,6 +21256,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="909">
+      <c r="A909" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B909" t="n">
+        <v>3405</v>
+      </c>
+      <c r="C909" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="D909" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="E909" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="F909" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="G909" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -21279,6 +21279,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="910">
+      <c r="A910" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B910" t="n">
+        <v>1972</v>
+      </c>
+      <c r="C910" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D910" t="n">
+        <v>3</v>
+      </c>
+      <c r="E910" t="n">
+        <v>3</v>
+      </c>
+      <c r="F910" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="G910" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -21302,6 +21302,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="911">
+      <c r="A911" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B911" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C911" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D911" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="E911" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="F911" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="G911" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -21325,6 +21325,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="912">
+      <c r="A912" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B912" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C912" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="D912" t="n">
+        <v>3</v>
+      </c>
+      <c r="E912" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="F912" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="G912" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -21166,22 +21166,22 @@
     </row>
     <row r="905">
       <c r="A905" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B905" t="n">
-        <v>19463</v>
+        <v>5</v>
       </c>
       <c r="C905" t="n">
         <v>3.04999995231628</v>
       </c>
       <c r="D905" t="n">
-        <v>2.78999996185303</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="E905" t="n">
-        <v>2.94000005722046</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="F905" t="n">
-        <v>3</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="G905" t="s">
         <v>7</v>
@@ -21189,22 +21189,22 @@
     </row>
     <row r="906">
       <c r="A906" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B906" t="n">
-        <v>5002</v>
+        <v>19463</v>
       </c>
       <c r="C906" t="n">
         <v>3.04999995231628</v>
       </c>
       <c r="D906" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="E906" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="F906" t="n">
         <v>3</v>
-      </c>
-      <c r="E906" t="n">
-        <v>3.03999996185303</v>
-      </c>
-      <c r="F906" t="n">
-        <v>3.04999995231628</v>
       </c>
       <c r="G906" t="s">
         <v>7</v>
@@ -21212,22 +21212,22 @@
     </row>
     <row r="907">
       <c r="A907" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B907" t="n">
-        <v>3508</v>
+        <v>5002</v>
       </c>
       <c r="C907" t="n">
-        <v>3.05999994277954</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="D907" t="n">
+        <v>3</v>
+      </c>
+      <c r="E907" t="n">
         <v>3.03999996185303</v>
       </c>
-      <c r="E907" t="n">
+      <c r="F907" t="n">
         <v>3.04999995231628</v>
-      </c>
-      <c r="F907" t="n">
-        <v>3.05999994277954</v>
       </c>
       <c r="G907" t="s">
         <v>7</v>
@@ -21235,22 +21235,22 @@
     </row>
     <row r="908">
       <c r="A908" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B908" t="n">
-        <v>300</v>
+        <v>3508</v>
       </c>
       <c r="C908" t="n">
-        <v>3.02999997138977</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="D908" t="n">
-        <v>3.02999997138977</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="E908" t="n">
-        <v>3.02999997138977</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="F908" t="n">
-        <v>3.02999997138977</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="G908" t="s">
         <v>7</v>
@@ -21258,22 +21258,22 @@
     </row>
     <row r="909">
       <c r="A909" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B909" t="n">
-        <v>3405</v>
+        <v>300</v>
       </c>
       <c r="C909" t="n">
-        <v>3.04999995231628</v>
+        <v>3.02999997138977</v>
       </c>
       <c r="D909" t="n">
-        <v>3.04999995231628</v>
+        <v>3.02999997138977</v>
       </c>
       <c r="E909" t="n">
-        <v>3.04999995231628</v>
+        <v>3.02999997138977</v>
       </c>
       <c r="F909" t="n">
-        <v>3.04999995231628</v>
+        <v>3.02999997138977</v>
       </c>
       <c r="G909" t="s">
         <v>7</v>
@@ -21281,22 +21281,22 @@
     </row>
     <row r="910">
       <c r="A910" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B910" t="n">
-        <v>1972</v>
+        <v>3405</v>
       </c>
       <c r="C910" t="n">
-        <v>3.03999996185303</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="D910" t="n">
-        <v>3</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="E910" t="n">
-        <v>3</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="F910" t="n">
-        <v>3.03999996185303</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="G910" t="s">
         <v>7</v>
@@ -21304,22 +21304,22 @@
     </row>
     <row r="911">
       <c r="A911" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B911" t="n">
-        <v>2500</v>
+        <v>1972</v>
       </c>
       <c r="C911" t="n">
         <v>3.03999996185303</v>
       </c>
       <c r="D911" t="n">
-        <v>2.96000003814697</v>
+        <v>3</v>
       </c>
       <c r="E911" t="n">
+        <v>3</v>
+      </c>
+      <c r="F911" t="n">
         <v>3.03999996185303</v>
-      </c>
-      <c r="F911" t="n">
-        <v>3.01999998092651</v>
       </c>
       <c r="G911" t="s">
         <v>7</v>
@@ -21327,22 +21327,22 @@
     </row>
     <row r="912">
       <c r="A912" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B912" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="C912" t="n">
-        <v>3.00999999046326</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="D912" t="n">
-        <v>3</v>
+        <v>2.96000003814697</v>
       </c>
       <c r="E912" t="n">
-        <v>3.00999999046326</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="F912" t="n">
-        <v>3.00999999046326</v>
+        <v>3.01999998092651</v>
       </c>
       <c r="G912" t="s">
         <v>7</v>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -24165,6 +24165,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="916">
+      <c r="A916" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B916" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C916" t="n">
+        <v>3</v>
+      </c>
+      <c r="D916" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="E916" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="F916" t="n">
+        <v>3</v>
+      </c>
+      <c r="G916" t="n">
+        <v>3</v>
+      </c>
+      <c r="H916" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -24191,6 +24191,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="917">
+      <c r="A917" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B917" t="n">
+        <v>2155</v>
+      </c>
+      <c r="C917" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="D917" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="E917" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="F917" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="G917" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="H917" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -24217,6 +24217,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="918">
+      <c r="A918" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B918" t="n">
+        <v>3305</v>
+      </c>
+      <c r="C918" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="D918" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="E918" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F918" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="G918" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="H918" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -24243,6 +24243,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="919">
+      <c r="A919" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B919" t="n">
+        <v>3315</v>
+      </c>
+      <c r="C919" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="D919" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="E919" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="F919" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="G919" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="H919" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -24321,6 +24321,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="922">
+      <c r="A922" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B922" t="n">
+        <v>5953</v>
+      </c>
+      <c r="C922" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D922" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E922" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F922" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G922" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="H922" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -21640,8 +21640,31 @@
       <c r="E925" t="n">
         <v>2.50999999046326</v>
       </c>
-      <c r="F925"/>
+      <c r="F925" t="n">
+        <v>2.4300000667572</v>
+      </c>
       <c r="G925" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B926" t="n">
+        <v>4976</v>
+      </c>
+      <c r="C926" t="n">
+        <v>2.47000002861023</v>
+      </c>
+      <c r="D926" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E926" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="F926"/>
+      <c r="G926" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -21663,8 +21663,31 @@
       <c r="E926" t="n">
         <v>2.46000003814697</v>
       </c>
-      <c r="F926"/>
+      <c r="F926" t="n">
+        <v>2.47000002861023</v>
+      </c>
       <c r="G926" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B927" t="n">
+        <v>4501</v>
+      </c>
+      <c r="C927" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="D927" t="n">
+        <v>2.4300000667572</v>
+      </c>
+      <c r="E927" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F927"/>
+      <c r="G927" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -21686,8 +21686,31 @@
       <c r="E927" t="n">
         <v>2.5</v>
       </c>
-      <c r="F927"/>
+      <c r="F927" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G927" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B928" t="n">
+        <v>2303</v>
+      </c>
+      <c r="C928" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D928" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="E928" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F928"/>
+      <c r="G928" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -21709,8 +21709,31 @@
       <c r="E928" t="n">
         <v>2.5</v>
       </c>
-      <c r="F928"/>
+      <c r="F928" t="n">
+        <v>2.48000001907349</v>
+      </c>
       <c r="G928" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B929" t="n">
+        <v>7602</v>
+      </c>
+      <c r="C929" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="D929" t="n">
+        <v>2.47000002861023</v>
+      </c>
+      <c r="E929" t="n">
+        <v>2.49000000953674</v>
+      </c>
+      <c r="F929"/>
+      <c r="G929" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -21739,6 +21739,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="930">
+      <c r="A930" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B930" t="n">
+        <v>750</v>
+      </c>
+      <c r="C930" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="D930" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E930" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F930" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="G930" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -24607,6 +24607,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="933">
+      <c r="A933" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B933" t="n">
+        <v>4623</v>
+      </c>
+      <c r="C933" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="D933" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E933" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="F933" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="G933" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="H933" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -24615,7 +24615,7 @@
         <v>4623</v>
       </c>
       <c r="C933" t="n">
-        <v>2.44000005722046</v>
+        <v>2.45000004768372</v>
       </c>
       <c r="D933" t="n">
         <v>2.34999990463257</v>
@@ -24630,6 +24630,32 @@
         <v>2.45000004768372</v>
       </c>
       <c r="H933" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B934" t="n">
+        <v>8513</v>
+      </c>
+      <c r="C934" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D934" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="E934" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F934" t="n">
+        <v>2.49000000953674</v>
+      </c>
+      <c r="G934" t="n">
+        <v>2.49000000953674</v>
+      </c>
+      <c r="H934" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -27464,6 +27464,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="935">
+      <c r="A935" t="s">
+        <v>9</v>
+      </c>
+      <c r="B935" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C935" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D935" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E935" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F935" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G935" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H935" t="n">
+        <v>1201</v>
+      </c>
+      <c r="I935" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -27493,6 +27493,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="936">
+      <c r="A936" t="s">
+        <v>9</v>
+      </c>
+      <c r="B936" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C936" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D936" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E936" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F936" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G936" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H936" t="n">
+        <v>0</v>
+      </c>
+      <c r="I936" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="s">
+        <v>9</v>
+      </c>
+      <c r="B937" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C937" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D937" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="E937" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F937" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="G937" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="H937" t="n">
+        <v>3202</v>
+      </c>
+      <c r="I937" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -27551,6 +27551,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="938">
+      <c r="A938" t="s">
+        <v>9</v>
+      </c>
+      <c r="B938" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C938" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D938" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E938" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F938" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="G938" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="H938" t="n">
+        <v>2082</v>
+      </c>
+      <c r="I938" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -27580,6 +27580,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="939">
+      <c r="A939" t="s">
+        <v>9</v>
+      </c>
+      <c r="B939" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C939" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="D939" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="E939" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="F939" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="G939" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="H939" t="n">
+        <v>2827</v>
+      </c>
+      <c r="I939" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -27609,6 +27609,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="940">
+      <c r="A940" t="s">
+        <v>9</v>
+      </c>
+      <c r="B940" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C940" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="D940" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="E940" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="F940" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="G940" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="H940" t="n">
+        <v>57824</v>
+      </c>
+      <c r="I940" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -27638,6 +27638,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="941">
+      <c r="A941" t="s">
+        <v>9</v>
+      </c>
+      <c r="B941" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C941" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D941" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E941" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="F941" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="G941" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="H941" t="n">
+        <v>29088</v>
+      </c>
+      <c r="I941" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -27667,6 +27667,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="942">
+      <c r="A942" t="s">
+        <v>9</v>
+      </c>
+      <c r="B942" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C942" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="D942" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="E942" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="F942" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="G942" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="H942" t="n">
+        <v>7713</v>
+      </c>
+      <c r="I942" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -27696,6 +27696,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="943">
+      <c r="A943" t="s">
+        <v>9</v>
+      </c>
+      <c r="B943" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C943" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D943" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="E943" t="n">
+        <v>2.68499994277954</v>
+      </c>
+      <c r="F943" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="G943" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="H943" t="n">
+        <v>902</v>
+      </c>
+      <c r="I943" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GM.MI.xlsx
+++ b/data/GM.MI.xlsx
@@ -27725,6 +27725,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="944">
+      <c r="A944" t="s">
+        <v>9</v>
+      </c>
+      <c r="B944" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C944" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D944" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="E944" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="F944" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G944" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="H944" t="n">
+        <v>3781</v>
+      </c>
+      <c r="I944" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
